--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/SOUTH_CAROLINA_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/SOUTH_CAROLINA_2017.xlsx
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C138">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C240">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C637">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C678">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C679">
